--- a/src/outputs/2ND SEM TTFINAL_1-cleaned.xlsx
+++ b/src/outputs/2ND SEM TTFINAL_1-cleaned.xlsx
@@ -1,24 +1,1453 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB0DBAC-3093-4D5F-B09A-BC849EBEBD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-AERO%70%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%70</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-AE%128%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%128</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-BME%136%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%136</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION  SKILLS II%Yeboah Philomena Ama Okyeso%ED1-CHE%120%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%120</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Bernard Ampong%ED1-COE%262%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%262</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-IND%83%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%83</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Patricia Gustafson-Asamoah%ED1-CE%245%Computer Based%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%245</t>
+  </si>
+  <si>
+    <t>PE 264%PRINCIPLES OF LAND SURVEYING AND HYDROGRAPHIC SCIENCE%Asante Cosmas Yaw%ED2-PE%95%NAF1/EA/VCR%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/30/25</t>
+  </si>
+  <si>
+    <t>CE 262%SOIL AND ROCKS MECHANICS LABORATORY%Dzikunu-Bansah Nancy Anataba Kyorku%ED2-CE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%35/35/35/35/35/28/27/20</t>
+  </si>
+  <si>
+    <t>CE 462%CONSTRUCTION MANAGEMENT%Obeng Daniel Atuah%ED4-CE%240%NEB-TF/NEB-SF/NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%80/80/30/55</t>
+  </si>
+  <si>
+    <t>AERO 452%AERODYNAMICS II%Bofah Kwasi Kete%ED4-AERO%61%RMB/206/N1%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%20/20/21</t>
+  </si>
+  <si>
+    <t>AME 368%AUTOMOTIVE SPARK-IGNITION ENGINES%Abu Frimpong Solomon%ED3-AUTO%40%206/304%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%22/18</t>
+  </si>
+  <si>
+    <t>BME 374%BIOMEDICAL OPTICS%Kotei Addison Eric Clement%ED3-BME%90%EA/A110/NAF1%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%27/27/36</t>
+  </si>
+  <si>
+    <t>COE 372%DIGITAL SYSTEMS DESIGN II%Boateng Kwame Osei%ED3-COE%265%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%38/38/38/38/38/28/27/20</t>
+  </si>
+  <si>
+    <t>COE 382%DIGITAL COMPUTER DESIGN%Boateng Kwame Osei%ED3-EE%29%A110%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%29</t>
+  </si>
+  <si>
+    <t>COE 486%INTRODUCTION TO VLSI%Agbemenu Andrew Selasi%ED4-EE%15%RMA%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%15</t>
+  </si>
+  <si>
+    <t>COE 486%VLSI CIRCUIT DESIGN%Agbemenu Andrew Selasi%ED4-COE%20%RMB%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%20</t>
+  </si>
+  <si>
+    <t>GE 272%ENGINEERING SURVEY II%Arko-Adjei Anthony%ED2-GEOM%132%VSLA/303/LT/RMA/304%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/30/21/21/20</t>
+  </si>
+  <si>
+    <t>CHE 470%PHARMACEUTICAL TECHNOLOGY%Johnson Raphael%ED4-CHE%71%NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%25/46</t>
+  </si>
+  <si>
+    <t>TE 374%COMPUTER NETWORKING%Kwasi Adu-Boahen Opare%ED3-TEL%140%303/LT/N1/N2/VSLA%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%30/25/25/20/40</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-EE%295%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%295</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Sarfo-Adu Kwasi%ED1-AUTO%85%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%85</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%125</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-PCE%56%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%56</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOM%103%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%103</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-METE%75%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%75</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-MSE%100%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%100</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-ME%225%Computer Based%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%225</t>
+  </si>
+  <si>
+    <t>MME 292%SEAMANSHIP%Larkai Francis Laako%ED2-MARI%37%304/206%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/17</t>
+  </si>
+  <si>
+    <t>GED 368%GIS APPLICATIONS%Appiah-Adjei Emmanuel Kwame%ED3-GEOL%154%PB001/PB014/PB201/PB214%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%39/39/38/38</t>
+  </si>
+  <si>
+    <t>GED 476%GROUNDWATER DEVELOPMENT%Ali Bukari%ED4-GEOL%95%303/LT/VSLA%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%28/25/42</t>
+  </si>
+  <si>
+    <t>BME 462%BIOMECHANICS II%Odame Prince%ED4-BME%87%NAF1/A110/VCR%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/27/20</t>
+  </si>
+  <si>
+    <t>CHE 350%MATERIALS SCIENCE%Patrick Boakye%ED3-CHE%105%PB020/PB008/PB208/PB212%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%35/25/25/20</t>
+  </si>
+  <si>
+    <t>CHE 350%MATERIALS SCIENCE%Anang Daniel Adjah%ED3-PCE%53%NEB-FF1%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%53</t>
+  </si>
+  <si>
+    <t>CHE 258%DRAWING FOR ENGINEERS%Darkwah Lawrence%ED2-CHE%160%NEB-TF/NEB-SF%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%80/80</t>
+  </si>
+  <si>
+    <t>CHE 258%DRAWING FOR ENGINEERS%Darkwah Lawrence%ED2-PCE%65%NAF1/EA%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/25</t>
+  </si>
+  <si>
+    <t>ME 478%PRODUCTION ENGINEERING II%Obeng George Yaw%ED4-ME%40%NEB-FF1%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40</t>
+  </si>
+  <si>
+    <t>AE 358%RENEWABLE ENERGY SYSTEMS AND MANAGEMENT%Kemausuor Francis%ED3-AE%101%NEB-FF2/NEB-SF%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%26/75</t>
+  </si>
+  <si>
+    <t>GED 252%STRATIGRAPHY%Amedjoe Godfrey Chiri%ED2-GEOL%150%VSLA/303/LT/RMA/RMB/304%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/30/20/20/20/20</t>
+  </si>
+  <si>
+    <t>MME 356%STRENGTH OF MARINE MATERIALS II%Adam Faisal Wahib%ED3-MARI%40%PB020%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40</t>
+  </si>
+  <si>
+    <t>ME 356%STRENGTH OF MATERIALS II%Tay Godwin Fabiola Kwaku%ED3-ME%222%PB001/PB014/PB201/PB214/PB008/PB212/PB208%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/25/20/25</t>
+  </si>
+  <si>
+    <t>MSE 458%PROCESS DYNAMICS AND CONTROL%Adjaottor Albert Amatey%ED4-MSE%60%206/RMA/RMB%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/20/20</t>
+  </si>
+  <si>
+    <t>MSE 458%PROCESS DYNANICS AND CONTROL%Adjaottor Albert Amatey%ED4-METE%55%EA/A110%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/25</t>
+  </si>
+  <si>
+    <t>PE 472%NATURAL GAS ENGINEERING II%Sarkodie Kwame%ED4-PE%99%NEB-FF2/NEB-TF%Monday, 6 July 2026%Session, 2 (10:00 AM - 11:00 AM)%29/70</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-MARI%46%Computer Based%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%46</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-PE%130%Computer Based%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%130</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-TEL%130%Computer Based%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%130</t>
+  </si>
+  <si>
+    <t>GE 472%LAND LAW AND REGISTRATION%Arko-Adjei Anthony%ED4-GEOM%93%VSLA/303/LT%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/30/23</t>
+  </si>
+  <si>
+    <t>METE 354%PHYSICAL METALLURGY OF NON-FERROUS METALS%Agyemang Frank Ofori%ED3-METE%87%NAF1/EA/A110%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/25/22</t>
+  </si>
+  <si>
+    <t>CE 352%STEEL AND TIMBER DESIGN%Mark Adom-Asamoah%ED3-CE%230%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%37/37/37/37/37/25/20</t>
+  </si>
+  <si>
+    <t>MME 492%SHIP OPERATION, REGULATION AND MANAGEMENT%Sackey Michael Nii%ED4-MARI%23%VCR%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%23</t>
+  </si>
+  <si>
+    <t>MSE 262%STRESS AND STRAIN ANALYSIS OF RIGID BODIES%Mensah-Darkwa Kwadwo%ED2-METE%57%NEB-FF1/NEB-FF2%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/17</t>
+  </si>
+  <si>
+    <t>MSE 262%STRESS AND STRAIN ANALYSIS OF RIGID BODIES%Mensah-Darkwa Kwadwo%ED2-MSE%83%N1/LT/RMB/N2%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%22/22/20/19</t>
+  </si>
+  <si>
+    <t>PL 252%PLANNING THE PHYSICAL ENVIRONMENT%Aboagye Prince Anokye%ED3-GEOM%122%NAF1/EA/A110/VCR%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%42/30/30/20</t>
+  </si>
+  <si>
+    <t>TE 262%ELECTROMAGNETIC FIELDS%Kwame Oteng Gyasi%ED2-EE%340%PB001/PB014/PB020/PB201/PB214/PB008/PB208/NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/30/30/50</t>
+  </si>
+  <si>
+    <t>TE 254%ELECTROMAGNETIC FIELD THEORY%Kwame Oteng Gyasi%ED2-TEL%175%VSLA/303/N1/N2/304/206/RMA%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/30/25/20/20/20/20</t>
+  </si>
+  <si>
+    <t>COE 254%OBJECT-ORIENTED PROGRAMMING%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED2-BME%80%NEB-TF%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%80</t>
+  </si>
+  <si>
+    <t>COE 254%OBJECT-ORIENTED PROGRAMMING%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED2-COE%255%NEB-SF/NEB-TF%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%170/85</t>
+  </si>
+  <si>
+    <t>PE 352%PETROLEUM GEOLOGY%Borkloe Julius Kwame%ED3-PE%80%RMA/304/206/RMB%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%20/20/20/20</t>
+  </si>
+  <si>
+    <t>IE 458%HUMAN FACTORS AND ERGONOMICS%Sackey Samuel Mensah%ED4-IND%69%N1/N2/303%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%24/18/27</t>
+  </si>
+  <si>
+    <t>CE 260%SOIL AND ROCK MECHANICS%Frederick Owusu-Nimo%ED2-CE%250%NEB-TF/NEB-SF/NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%85/85/30/50</t>
+  </si>
+  <si>
+    <t>CE 260%SOIL AND ROCK MECHANICS%Owusu-Nimo Frederick%ED2-GEOM%132%PB201/PB214/PB008/PB208%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/28/28</t>
+  </si>
+  <si>
+    <t>MSE 352%GLASS AND CEMENT TECHNOLOGIES%Andrews Anthony%ED3-MSE%85%N1/206/304/N2%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%25/20/20/20</t>
+  </si>
+  <si>
+    <t>CHE 156%PHYSICAL CHEMISTRY FOR ENGINEERS%Anang Daniel Adjah%ED1-CHE%120%EA/A110/VCR/NAF1%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%28/28/25/40</t>
+  </si>
+  <si>
+    <t>AE 196%ENGINEERING WORKSHOP PRACTICE%Michael Adusei-Bonsu%ED1-AE%128%VSLA/303/LT/RMA/RMB%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/28/20/20/20</t>
+  </si>
+  <si>
+    <t>BME 364%MEDICAL IMAGING I%Kotei Addison Eric Clement%ED3-BME%90%NAF1/EA/A110%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/25/25</t>
+  </si>
+  <si>
+    <t>CHE 466%PULP AND PAPER TECHNOLOGY%Rockson Mizpah Ama Dziedzorm%ED4-CHE%70%NEB-FF1/NEB-FF2%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%50/20</t>
+  </si>
+  <si>
+    <t>TE 384%SWITCHING ENGINEERING IN COMMUNICATION%Obour Agyekum Kwame Opuni-Boachie%ED3-EE%10%VCR%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%10</t>
+  </si>
+  <si>
+    <t>TE 356%SWITCHING ENGINEERING IN COMMUNICATION%Agyekum Kwame Agyeman-Prempeh%ED3-TEL%140%PB001/PB014/PB020/PB008%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/26</t>
+  </si>
+  <si>
+    <t>AME 384%MICROPROCESSORS AND MECHATRONICS APPLICATIONS%Sackey Michael Nii%ED3-AUTO%40%206/304%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/20</t>
+  </si>
+  <si>
+    <t>ME 258%COMPUTER-AIDED DESIGN AND MODELLING%Sackey Michael Nii%ED2-AERO%75%NEB-TF%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%75</t>
+  </si>
+  <si>
+    <t>IE 366%ADVANCED MANUFACTURING TECHNOLOGY I%Takyi Gabriel%ED3-IND%70%NEB-SF%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%70</t>
+  </si>
+  <si>
+    <t>AE 482%FARM MACHINERY DESIGN%Aveyire Joseph%ED4-AE%103%LT/RMA/RMB/VSLA%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%25/20/18/40</t>
+  </si>
+  <si>
+    <t>CE 452%COMPUTER APPLICATIONS IN CIVIL ENGINEERING%Ayeh Felix Jojo Fianko%ED4-CE%240%PB001/PB014/PB020/PB201/PB214/PB212/PB208%Monday, 6 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/38/38/25/25</t>
+  </si>
+  <si>
+    <t>GED 262%INTRODUCTION TO SOIL MECHANICS%Amenuvor Andrew Cudzo%ED2-GEOL%150%PB201/PB214/PB020/PB001%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%38/38/37/37</t>
+  </si>
+  <si>
+    <t>GED 164%COMPUTER APPLICATIONS%Albert Kwame Kwaw%ED1-GEOL%125%VSLA/N2/304/RMA/N1%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/20/20/20/22</t>
+  </si>
+  <si>
+    <t>PE 262%COMPUTER PROGRAMMING IN OIL AND GAS%Sokama-Neuyam Yen Adams%ED2-PE%95%PB014/PB208/PB008%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%38/30/27</t>
+  </si>
+  <si>
+    <t>CE 154%PROPERTIES OF CIVIL ENGINEERING MATERIAL%Kankam Charles Kwame%ED1-CE%245%NEB-TF/NEB-FF1/NEB-FF2/NEB-SF%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%82/51/30/82</t>
+  </si>
+  <si>
+    <t>GED 370%FOUNDATION ENGINEERING%Amenuvor Andrew Cudzo%ED3-GEOL%154%VSLA/303/LT/304/RMA/RMB%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/30/25/20/20/20</t>
+  </si>
+  <si>
+    <t>COE 458%ROBOTICS AND COMPUTER VISION%Klogo Griffith Selorm%ED4-COE%45%NEB-FF1%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45</t>
+  </si>
+  <si>
+    <t>CHE 464%ADSORPTION SEPARATION PROCESS TECHNOLOGY%Ohemeng-Boahen Godfred%ED4-PCE%40%N2/RMB%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/20</t>
+  </si>
+  <si>
+    <t>CHE 362%SILICATE TECHNOLOGY II%Momade Zsuzsanna Gál%ED3-CHE%15%PB212%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%15</t>
+  </si>
+  <si>
+    <t>ME 366%HEAT TRANSFER%Forson Francis Kofi%ED3-ME%222%PB001/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%38/38/38/38/25/25/20</t>
+  </si>
+  <si>
+    <t>ME 366%HEAT TRANSFER%Forson Francis Kofi%ED3-AERO%76%NEB-TF%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%76</t>
+  </si>
+  <si>
+    <t>ME 366%HEAT TRANSFER%Forson Francis Kofi%ED3-AE%101%EA/A110/NAF1%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/30/41</t>
+  </si>
+  <si>
+    <t>ME 366%HEAT TRANSFER%Forson Francis Kofi%ED3-MARI%40%PB020%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40</t>
+  </si>
+  <si>
+    <t>MSE 154%OPTICAL AND THERMAL BEHAVIOUR OF MATERIALS%Nartey Martinson Addo%ED1-METE%75%303/N1/LT%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%28/25/22</t>
+  </si>
+  <si>
+    <t>MSE 154%OPTICAL AND THERMAL BEHAVIOUR OF MATERIALS%Nartey Martinson Addo%ED1-MSE%100%NEB-FF2/NEB-SF%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%25/75</t>
+  </si>
+  <si>
+    <t>GED 452%ADVANCED ENGINEERING GEOLLOGY%Gidigasu Solomon Senyo Robert%ED4-GEOL%95%NAF1/EA/A110%Monday, 6 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/28/27</t>
+  </si>
+  <si>
+    <t>ME 456%INTRODUCTION TO FINITE ELEMENT%Andoh Prince Yaw%ED4-AUTO%32%Computer Based%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%32</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-IND%80%NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/50</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-MARI%37%N1/206%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%20/17</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-ME%240%PB001/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%39/39/39/39/30/30/24</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-AUTO%82%NAF1/EA/VCR%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%35/25/22</t>
+  </si>
+  <si>
+    <t>TE 262%ELECTROMAGNETIC FIELDS%Yeboah-Akowuah Bright%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/40/40/40/40/28/27</t>
+  </si>
+  <si>
+    <t>METE 252%METALLURGICAL RATE PROCESSES/SURFACE PHENOMENA%Patrick Aggrey%ED2-METE%57%PB212/PB020%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%20/37</t>
+  </si>
+  <si>
+    <t>ME 168%COMPUTER PROGRAMMING FOR ENGINEERS%Dzebre Denis Edem Kwame%ED1-IND%83%NEB-SF%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%83</t>
+  </si>
+  <si>
+    <t>ME 168%COMPUTER PROGRAMMING FOR ENGINEERS%Dzebre Denis Edem Kwame%ED1-MARI%46%NAF1%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%46</t>
+  </si>
+  <si>
+    <t>ME 168%COMPUTER PROGRAMMING FOR ENGINEERS%Tay Godwin Fabiola Kwaku%ED1-AERO%70%A110/EA/VCR%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%25/25/20</t>
+  </si>
+  <si>
+    <t>ME 168%COMPUTER PROGRAMMING FOR ENGINEERS%Tay Godwin Fabiola Kwaku%ED1-ME%225%VSLA/303/LT/N1/RMB/304/206/N2/RMA%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%42/30/25/25/20/20/20/20/20</t>
+  </si>
+  <si>
+    <t>PCE 354%PETROCHEMICAL ENGINEERING LABORATORY II%Bonsu Jude Kwaku%ED3-PCE%53%NEB-TF%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%53</t>
+  </si>
+  <si>
+    <t>PE 366%HEALTH SAFETY AND ENVIRONMENT%Adjei Stephen%ED3-PE%80%NEB-SF%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%80</t>
+  </si>
+  <si>
+    <t>PE 474%PIPELINE ENGINEERING%Adjei Stephen%ED4-PE%99%NEB-TF%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%99</t>
+  </si>
+  <si>
+    <t>MSE 154%PRINCIPLES OF MATERIAL SCIENCE%Agyemang Frank Ofori%ED2-BME%80%NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/50</t>
+  </si>
+  <si>
+    <t>ME 282%MECHANICAL ENGINEERING MATERIALS II%Agyemang Frank Ofori%ED2-AE%155%VSLA/303/304/LT/RMA/RMB/N2%Monday, 6 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/25/20/20/17/17/16</t>
+  </si>
+  <si>
+    <t>PE 256%REGIONAL GEOLOGY%Quaye Jonathan Atuquaye%ED2-PE%95%NEB-TF%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%95</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Kwegyir Daniel%ED1-CE%245%NEB-SF/NEB-TF%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%170/75</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Yaw Opoku Mensah Sekyere%ED1-CHE%120%A110/EA/VCR/NAF1%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%28/28/24/40</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Nicholas Kwesi Prah II%ED1-MARI%46%NEB-FF1%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%46</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Kwegyir Daniel%ED1-AUTO%85%PB001/PB014/PB208%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%35/35/15</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Twumasi Elvis%ED1-PE%130%PB201/PB214/PB008/PB212%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%39/39/28/24</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Nicholas Kwesi Prah II%ED1-AERO%70%303/LT/N1%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%28/22/20</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Twumasi Elvis%ED1-PCE%56%PB020/PB212%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%37/19</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Yaw Opoku Mensah Sekyere%ED1-EE%295%PB001/PB014/PB020/PB201/PB214/PB208/PB008/NEB-FF2%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%38/38/38/38/38/30/30/25</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Affum Emmanuel Ampoma%ED1-TEL%130%VSLA/RMA/RMB/304/206%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/22/22/20/21</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Nicholas Kwesi Prah II%ED1-AE%128%NAF1/A110/EA/VCR%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/30/23</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Yaw Opoku Mensah Sekyere%ED1-ME%225%VSLA/303/LT/N1/RMB/304/206/N2/RMA%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%42/30/25/25/22/20/22/20/21</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Nicholas Kwesi Prah II%ED1-IND%83%NEB-FF2/NEB-FF1%Tuesday, 7 July 2026%Session, 1 (8:15 AM - 9:15 AM)%30/53</t>
+  </si>
+  <si>
+    <t>EE 252%ELECTRICAL ENGINEERING MACHINES%Yaw Opoku Mensah Sekyere%ED2-AE%155%NEB-SF/NEB-TF/NEB-FF1%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%65/40/50</t>
+  </si>
+  <si>
+    <t>EE 252%ELECTRICAL ENGINEERING MACHINES%Yaw Opoku Mensah Sekyere%ED3-ME%222%VSLA/303/LT/N1/RMB/304/206/N2/RMA%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%42/30/25/25/20/20/20/20/20</t>
+  </si>
+  <si>
+    <t>EE 172%ELECTRICAL MACHINES%Asigri Peter%ED1-COE%262%PB001/PB014/PB020/PB201/PB214/PB212/PB208/PB008%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/38/22/25/25</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Kwegyir Daniel%ED1-GEOL%125%NEB-TF%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%125</t>
+  </si>
+  <si>
+    <t>EE 152%BASIC ELECTRONICS%Kwegyir Daniel%ED1-GEOM%103%NEB-SF%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%103</t>
+  </si>
+  <si>
+    <t>GE 354%SATELLITE SURVEYING%Andam-Akorful Samuel Ato%ED3-GEOM%122%NAF1/A110/EA/VCR%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%42/28/28/24</t>
+  </si>
+  <si>
+    <t>PE 450%RESERVOIR RECOVERY TECHNIQUES%Adenutsi Caspar Daniel%ED4-PE%99%303/N1/NAF1%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/25/44</t>
+  </si>
+  <si>
+    <t>MME 264%MARINE MECHANISMS, SYSTHESIS AND ANALYSIS%Ampofo Joshua%ED2-MARI%37%PB020%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%37</t>
+  </si>
+  <si>
+    <t>ME 264%MECHANISMS SYNTHESIS AND ANALYSIS I%Ampofo Joshua%ED2-ME%240%PB001/PB014/PB201/PB214/PB008/PB208/PB212%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%39/39/39/39/30/30/24</t>
+  </si>
+  <si>
+    <t>ME 264%MECHANISMS SYNTHESIS AND ANALYSIS I%Ampofo Joshua%ED2-AERO%75%VSLA/LT/206%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/20/15</t>
+  </si>
+  <si>
+    <t>ME 264%MECHANISMS SYNTHESIS AND ANALYSIS I%Ampofo Joshua%ED2-IND%80%NEB-FF2/NEB-FF1%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/50</t>
+  </si>
+  <si>
+    <t>ME 264%MECHANISMS SYNTHESIS AND ANALYSIS I%Ampofo Joshua%ED2-AUTO%82%304/N2/RMA/RMB%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/20/21/21</t>
+  </si>
+  <si>
+    <t>CHE 354%SIMULTANEOUS HEAT/MASS TRANSFER%Dogbe Eunice Sefakor Aku%ED3-CHE%105%EA/A110/VCR/NEB-FF2%Tuesday, 7 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/30/20/25</t>
+  </si>
+  <si>
+    <t>EE 462%ELECTRIC DRIVES%Effah Francis Boafo%ED4-EE%189%PB001/PB014/PB020/PB201/PB214 %Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%38/38/38/38/37</t>
+  </si>
+  <si>
+    <t>GED 352%PRINCIPLES OF GEOLCHEMISTRY%Gawu Simon Kafui Yawo%ED3-GEOL%154%VSLA/303/LT/N1/N2/RMA %Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/28/23/23/20/20</t>
+  </si>
+  <si>
+    <t>AE 460%MAINTENANCE AND REPAIRS OF AGRIC. MACHINERY%Bobobee Emmanuel Yaovi Hunnuor%ED4-AE%103%A110/EA/NAF1%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%30/30/43</t>
+  </si>
+  <si>
+    <t>CHE 468%ENVIRONMENTAL ENG. TECHNOLOGY%Afotey Benjamin%ED4-CHE%54%PB208/PB212%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%30/24</t>
+  </si>
+  <si>
+    <t>CE 458%WATER RESOURCES ENGINEERING II%Anornu Geophrey Kwame%ED4-CE%105%NAF1/EA/A110%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/30/30</t>
+  </si>
+  <si>
+    <t>IE 452%AUTOMATION AND PRODUCTION SYSTEM%Sackey Samuel Mensah%ED4-IND%69%RMB/206/304%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%24/24/21</t>
+  </si>
+  <si>
+    <t>EE 360%HIGH VOLTAGE ENGINEERING%Asigri Peter%ED3-EE%185%VSLA/303/LT/N1/N2/RMA/RMB%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/30/25/25/20/20/20</t>
+  </si>
+  <si>
+    <t>EE 258%POWER SUPPLY ELECTRONICS%Effah Francis Boafo%ED2-EE%340%PB001/PB014/PB020/PB201/PB214/PB008/PB212/NEB-FF2/NEB-FF1%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/25/30/55</t>
+  </si>
+  <si>
+    <t>ME 482%MECHANICAL ENGINEERING MATERIALS III%Sackey Samuel Mensah%ED4-ME%55%PB208/PB008%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%28/27</t>
+  </si>
+  <si>
+    <t>TE 258%MICROPROCESSORS%Agyemang Justice Owusu%ED2-TEL%175%NEB-TF%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%175</t>
+  </si>
+  <si>
+    <t>MSE 260%PHASE TRANSFORMATIONS%Gikunoo Emmanuel%ED2-MSE%83%NEB-SF%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%83</t>
+  </si>
+  <si>
+    <t>MSE 260%PHASE TRANSFORMATIONS%Gikunoo Emmanuel%ED2-METE%57%NEB-FF2/NEB-FF1%Tuesday, 7 July 2026%Session, 3 (11:45 AM - 12:45 PM)%20/37</t>
+  </si>
+  <si>
+    <t>MME 494%MARINE MAINTENANCE ENGINEERING%Peter Oppong Tawiah %ED4-MARI%23%VCR%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%23</t>
+  </si>
+  <si>
+    <t>CE 256%FLUID MECHANICS%Anornu Geophrey Kwame%ED2-CE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB212/PB208%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/38/38/20/20/20</t>
+  </si>
+  <si>
+    <t>CE 256%FLUID MECHANICS%Anornu Geophrey Kwame%ED2-GEOL%150%VSLA/303/LT/N1/N2/RMB%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%41/25/22/22/20/20</t>
+  </si>
+  <si>
+    <t>ME 392%INDUSTRIAL ENGINEERING AND ERGONOMICS%Mensah Lena Dzifa%ED3-AERO%76%A110/EA/VCR%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%28/28/20</t>
+  </si>
+  <si>
+    <t>ME 292%INDUSTRIAL ENGINEERING AND ERGONOMICS%Mensah Lena Dzifa%ED2-ME%240%NEB-SF/NEB-TF/NEB-FF1/NEB-FF2%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%80/80/50/30</t>
+  </si>
+  <si>
+    <t>AME 392%INDUSTRIAL ENGINEERING AND ERGONOMICS%Mensah Lena Dzifa%ED3-AUTO%40%NAF1%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40</t>
+  </si>
+  <si>
+    <t>MME 392%MARINE INDUSTRIAL ENGINEERING AND ERGONOMICS%Mensah Lena Dzifa%ED3-MARI%40%N2/RMB%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/20</t>
+  </si>
+  <si>
+    <t>BME 366%BIOSIGNAL PROCESSES AND ANALYSIS%Adjei Prince Ebenezer%ED3-BME%90%NAF1/EA/A110%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/25/25</t>
+  </si>
+  <si>
+    <t>CHE 256%HEAT TRANSPORT PROCESSES%Momade Zsuzsanna Gál%ED2-CHE%160%VSLA/303/LT/N1/N2/RMA%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%44/28/24/24/20/20</t>
+  </si>
+  <si>
+    <t>COE 354%OPERATING SYSTEMS%Kommey Benjamin%ED3-COE%265%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/38/38/28/27/20</t>
+  </si>
+  <si>
+    <t>CE 356%HYDRAULIC ENGINEERING%Adjei Kwaku Amaning%ED3-CE%230%NEB-SF/NEB-TF/NEB-FF2/NEB-FF1%Tuesday, 7 July 2026%Session, 4 (1:30 PM - 2:30 PM)%80/80/25/45</t>
+  </si>
+  <si>
+    <t>METE 452%ELECTROMETALLURGY%Agbe Henry%ED4-METE%55%RMB/206/304%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%23/22/20</t>
+  </si>
+  <si>
+    <t>GE 372%ANALYSIS OF ERRORS%Collins Fosu%ED3-GEOM%122%NAF1/A110/EA/VCR%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/28/28/23</t>
+  </si>
+  <si>
+    <t>CE 156%ELEMENTARY FLUIDS MECHANICS%Gyamfi Charles%ED1-CE%245%NEB-SF/NEB-FF1/NEB-FF2/NEB-TF%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%85/55/30/75</t>
+  </si>
+  <si>
+    <t>CE 156%ELEMENTARY FLUIDS MECHANICS%Gyamfi Charles%ED1-GEOL%125%PB001/PB014/PB020/PB008%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%35/35/35/20</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Opoku Richard%ED1-METE%75%NEB-SF%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%75</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Boahen Samuel%ED1-PCE%56%PB212/PB201%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%25/31</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-CHE%120%NAF1/EA/A110/VCR%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/28/28/21</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-AE%128%PB008/PB001/PB014/PB020%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/34/34/30</t>
+  </si>
+  <si>
+    <t>ME 164%STATICS OF SOLID MECHANICS%Oppong David Kofi%ED1-AUTO%85%303/LT/VSLA%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%25/20/40</t>
+  </si>
+  <si>
+    <t>COE 456%SECURE NETWORK SYSTEMS%Tchao Eric Tutu%ED4-COE%90%N1/N2/RMA/206%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%24/20/23/23</t>
+  </si>
+  <si>
+    <t>GED 454%ENVIRONMENTAL GEOLLOGY%Foli Gordon%ED4-GEOL%95%PB214/PB208/PB212%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/30/25</t>
+  </si>
+  <si>
+    <t>BME 166%BIOCHEMISTRY%Charles Apprey%ED1-BME%136%PB214/PB201/PB208/NEB-FF2%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/30/26</t>
+  </si>
+  <si>
+    <t>PCE 352%SEPARATION PROCESSES II%Augustine Ntiamoah%ED3-PCE%53%NEB-FF1%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%53</t>
+  </si>
+  <si>
+    <t>METE 352%HYDROMETALLURGICAL APPLICATIONS%Agbe Henry%ED3-METE%87%304/RMA/RMB/N1%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/22/22/23</t>
+  </si>
+  <si>
+    <t>ME 164%ENGINEERING MECHANICS I:STATICS%Amoabeng Kofi Owura%ED1-IND%83%NEB-FF1/NEB-FF2%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%53/30</t>
+  </si>
+  <si>
+    <t>ME 164%ENGINEERING MECHANICS I:STATICS%Amoabeng Kofi Owura%ED1-MARI%46%RMA/RMB%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%24/22</t>
+  </si>
+  <si>
+    <t>CHE 456%PROCESS CONTROL AND SIMULATION%Baah-Ennumh Emmanuel Kwaku%ED4-CHE%114%EA/A110/VCR/NAF1%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%28/28/20/38</t>
+  </si>
+  <si>
+    <t>CHE 456%PROCESS CONTROL AND SIMULATION%Baidoo Martina Francisca%ED4-PCE%55%PB208/PB212%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/25</t>
+  </si>
+  <si>
+    <t>CHE 352%CHEMICAL REACTION ENGINEERING%Bonsu Jude Kwaku%ED3-CHE%105%N1/303/304/VSLA%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%20/25/20/40</t>
+  </si>
+  <si>
+    <t>BME 286%ANATOMY AND PHYSIOLOGY FOR ENGINEERS II%Agyapong Dorothy Araba Yakoba%ED2-BME%80%NEB-FF1/NEB-FF2%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%55/25</t>
+  </si>
+  <si>
+    <t>GED 364%STRUCTURAL GEOLOGY%Wilson Matthew Coffie%ED3-GEOL%154%PB001/PB014/PB020/PB201%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/40/38/36</t>
+  </si>
+  <si>
+    <t>CE 464%ENVIRONMENTAL QUALITY ENGINEERING II%Appiah-Effah Eugene%ED4-CE%115%PB214/PB001/PB014%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/38/37</t>
+  </si>
+  <si>
+    <t>AE 360%RURAL ENGINEERING%Mensah Ebenezer%ED3-AE%101%PB214/PB201/PB008%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%38/38/25</t>
+  </si>
+  <si>
+    <t>ME 158%ENGINEERING GRAPHICS%Sackey Michael Nii%ED1-AERO%70%PB020/PB008%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/30</t>
+  </si>
+  <si>
+    <t>PSYC 154%INTRODUCTION TO PSYCHOLOGY%Sarfo Fordjour Elizabeth Anokyewaa%ED1-TEL%130%NAF1/EA/A110/VCR%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%45/30/30/25</t>
+  </si>
+  <si>
+    <t>MSE 360%MECHANICS OF MATERIALS%Mensah-Darkwa Kwadwo%ED3-MSE%85%LT/RMB/RMA/206%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%25/20/20/20</t>
+  </si>
+  <si>
+    <t>EE 158%INTRO TO PYTHON &amp; COMPUTER NETWORKING%Charles Mawutor Adrah%ED1-EE%340%NEB-TF/NEB-SF%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%170/170</t>
+  </si>
+  <si>
+    <t>TE 452%TELECOMMUNICATION POLICY AND REGULATION%Kingsford Sarkodie Obeng Kwakye%ED4-TEL%138%VSLA/303/LT/N1/304%Tuesday, 7 July 2026%Session, 6 (5:00 PM - 6:00 PM)%44/29/25/25/15</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Asamoah Joshua Kiddy Kwasi%ED1-BME%136%Computer Based%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%136</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Asamoah Joshua Kiddy Kwasi%ED1-AE%128%Computer Based%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%128</t>
+  </si>
+  <si>
+    <t>GED 162%BASIC GEOLOGY%Gawu Simon Kafui Yawo%ED1-METE%75%VSLA/RMA/RMB%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/20/15</t>
+  </si>
+  <si>
+    <t>COE 288%CIRCUIT THEORY%Yeboah-Akowuah Bright%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%37/37/37/37/37/25/25/20</t>
+  </si>
+  <si>
+    <t>COE 288%CIRCUIT THEORY%Yeboah-Akowuah Bright%ED2-BME%80%NEB-FF2/NEB-FF1%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%30/50</t>
+  </si>
+  <si>
+    <t>EE 272%DIGITAL SYSTEMS%Opoku Daniel%ED2-EE%340%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212/NEB-FF1%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/40/40/40/40/30/30/25/55</t>
+  </si>
+  <si>
+    <t>CE 272%PRINCIPLE OF DESIGN%Ayeh Felix Jojo Fianko%ED2-CE%250%VSLA/303/LT/N1/RMA/RMB/206/N2/304/VCR%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/25/25/24/21/20/202/20/20</t>
+  </si>
+  <si>
+    <t>PE 156%PHYSICAL CHEMISTRY FOR ENGINEERS%Boakye Patrick%ED1-PE%130%NAF1/A110/EA/VCR%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/30/25</t>
+  </si>
+  <si>
+    <t>CHE 156%PHYSICAL CHEMISTRY FOR ENGINEERS%Boakye Patrick%ED1-PCE%56%N1/N2/304%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%20/20/16</t>
+  </si>
+  <si>
+    <t>TE 468%MILLIMETERWAVE TECHNOLOGY%Abdul-Rahman Ahmed%ED4-TEL%33%NAF1%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%33</t>
+  </si>
+  <si>
+    <t>CHE 368%FOOD PROCESSING TECHNOLOGY%Anang Daniel Adjah%ED3-CHE%50%303/LT %Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%28/22</t>
+  </si>
+  <si>
+    <t>PCE 350%KINETICS AND REACTIONS ENGINEERING%Augustine Ntiamoah%ED3-PCE%53%A110/EA%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%28/25</t>
+  </si>
+  <si>
+    <t>AME 252%AUTOMOTIVE ELECTRICAL SYSTEMS AND ELECTRONICS%Ayetor Godwin Kafui Kwesi%ED2-AUTO%82%NEB-TF%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%82</t>
+  </si>
+  <si>
+    <t>TE 158%INTRODUCTION TO PROGRAMMING - I%Agyemang Justice Owusu%ED1-TEL%130%NEB-TF/NEB-SF%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%65/65</t>
+  </si>
+  <si>
+    <t>ME 374%MACHINE DESIGN II%Afriyie Nyarko Frank Kwabena%ED3-AE%101%NEB-SF%Wednesday, 8 July 2026%Session, 1 (8:15 AM - 9:15 AM)%101</t>
+  </si>
+  <si>
+    <t>ENGL 264%LITERATURE IN ENGLISH II%Yeboah Philomena Ama Okyeso%ED2-AE%155%VSLA/206/LT/N1/N2/304%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%41/24/25/25/20/20</t>
+  </si>
+  <si>
+    <t>ENGL 264%LITERATURE IN ENGLISH II%Yeboah Philomena Ama Okyeso%ED2-AERO%75%RMA/RMB/303%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%24/24/27</t>
+  </si>
+  <si>
+    <t>ENGL 264%LITERATURE IN ENGLISH II%Yeboah Philomena Ama Okyeso%ED2-GEOM%132%NEB-SF/NEB-TF%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%70/62</t>
+  </si>
+  <si>
+    <t>ENGL 264%LITERATURE IN ENGLISH II%Yeboah Philomena Ama Okyeso%ED2-IND%80%NEB-FF1/NEB-FF2%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%50/30</t>
+  </si>
+  <si>
+    <t>MSE 254%INTRODUCTION TO CERAMICS%Andrews Anthony%ED2-MSE%83%NEB-SF%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%83</t>
+  </si>
+  <si>
+    <t>CE 368% HIGHWAY ENGINEERING%Ababio-Donkor Augustus%ED3-GEOM%122%NAF1/EA/A110/VCR%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%42/30/30/20</t>
+  </si>
+  <si>
+    <t>CE 478%GROUND ENGINEERING%Samuel Innocent Kofi Ampadu%ED4-CE%60%PB208/PB008%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/30</t>
+  </si>
+  <si>
+    <t>CE 478%GROUND ENGINEERING%Samuel Innocent Kofi Ampadu%ED4-GEOL%2%RMA%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%2</t>
+  </si>
+  <si>
+    <t>EE 188%ELECTRICAL MEASUREMENTS &amp; INSTRUMENTATION%Nicholas Kwesi Prah II%ED1-EE%295%PB001/PB014/PB020/PB201/PB214/PB208/PB212/NEB-FF1%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/38/28/25/52</t>
+  </si>
+  <si>
+    <t>CHE 250%STRENGTH OF MATERIALS FOR CHEMICAL ENGINEERS%Anang Daniel Adjah%ED2-CHE%160%VSLA/304/LT/N1/N2/303%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%45/20/25/25/20/25</t>
+  </si>
+  <si>
+    <t>CHE 250%STRENGTH OF MATERIALS FOR CHEMICAL ENGINEERS%Baidoo Martina Francisca%ED2-PCE%65%NEB-TF%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%65</t>
+  </si>
+  <si>
+    <t>GED 152%BASIC MINERAL SCIENCE%Appiah-Adjei Emmanuel Kwame%ED1-GEOL%125%EA/A110/VCR/NAF1%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/30/25/40</t>
+  </si>
+  <si>
+    <t>CE 364%ENVIRONMENTAL QUALITY ENGINEERING%Appiah-Effah Eugene%ED3-CE%230%PB001/PB014/PB020/PB201/PB214/PB008/PB212%Wednesday, 8 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/38/20/20</t>
+  </si>
+  <si>
+    <t>ME 362%VIBRATIONS I%Adam Faisal Wahib%ED3-AERO%76%EA/A110/VCR %Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%28/28/20</t>
+  </si>
+  <si>
+    <t>ME 362%VIBRATIONS I%Adam Faisal Wahib%ED3-ME%222%NEB-SF/NEB-FF1/NEB-FF2/NEB-TF%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%80/50/30/62</t>
+  </si>
+  <si>
+    <t>ME 362%VIBRATIONS I%Adam Faisal Wahib%ED3-MARI%40%PB001%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40</t>
+  </si>
+  <si>
+    <t>AME 362%VIBRATIONS FOR AUTOMOBILE ENGINEERS%Adam Faisal Wahib%ED3-AUTO%40%PB014%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40</t>
+  </si>
+  <si>
+    <t>ME 494%MAINTENANCE ENGINEERING%Peter Oppong Tawiah %ED4-ME%135%VSLA/303/LT/N1/N2%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/30/25/25/15</t>
+  </si>
+  <si>
+    <t>ME 494%MAINTENANCE ENGINEERING%Peter Oppong Tawiah %ED4-IND%69%PB201/PB214%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%35/34</t>
+  </si>
+  <si>
+    <t>SES 172%AQUATIC STROKES DEVELOPMENT AND REFINEMENT%Afrifa Daniel%ED2-MARI%37%PB020 %Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%37</t>
+  </si>
+  <si>
+    <t>MSE 354%PHYSICAL METALLURGY OF FERROUS METALS%Kwofie Samuel%ED3-MSE%85%NEB-TF%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%85</t>
+  </si>
+  <si>
+    <t>METE 362%PHYSICAL METALLURGY OF FERROUS METALS%Kwofie Samuel%ED3-METE%87%RMA/RMB/304/206%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%23/22/20/22</t>
+  </si>
+  <si>
+    <t>IE 356%RELIABILITY ENGINEERING%Takyi Gabriel%ED3-IND%70%PB008/PB208/PB212%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%25/25/20</t>
+  </si>
+  <si>
+    <t>PE 358%PETROLEUM PRODUCTION ENGINEERING II%Sarkodie Kwame%ED3-PE%80%NEB-SF%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%80</t>
+  </si>
+  <si>
+    <t>PCE 450%PETROLEUM REFINING ENGINEERING%Kwao-Boateng Emmanuela%ED4-PCE%55%NEB-FF1%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%55</t>
+  </si>
+  <si>
+    <t>PCE 464%REFINING PROCESSES TECHNOLOGY%Kwao-Boateng Emmanuela%ED4-CHE%50%VCR/NAF1%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%20/30</t>
+  </si>
+  <si>
+    <t>COE 480%FAULT DIAGNOSIS AND FAILURE TOLERANCE%Agbemenu Andrew Selasi%ED4-COE%70%EA/A110/NAF1%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%20/20/30</t>
+  </si>
+  <si>
+    <t>COE 358%EMBEDDED SYSTEMS%Kommey Benjamin%ED3-COE%265%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%38/38/38/38/38/27/27/21</t>
+  </si>
+  <si>
+    <t>COE 358%EMBEDDED SYSTEMS%Kommey Benjamin%ED3-BME%90%N1/N2/RMA/206%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%25/20/23/22</t>
+  </si>
+  <si>
+    <t>PE 258%PETROLEUM ENGINEERING THERMODYNAMICS II%Sokama-Neuyam Yen Adams%ED2-PE%95%VSLA/LT/303%Wednesday, 8 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/25/25</t>
+  </si>
+  <si>
+    <t>MSE 454%SURFACE TREATMENT OF MATERIALS%Andrews Anthony%ED4-MSE%60%RMB/N2/LT%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/20/20</t>
+  </si>
+  <si>
+    <t>BME 454%MEDICAL DEVICE REGULATION%Acquah Isaac%ED4-BME%87%NEB-FF1/NEB-FF2%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%56/31</t>
+  </si>
+  <si>
+    <t>GE 152%REPRODUCTION CARTOGRAPHY%Quaye-Ballard Jonathan Arthur%ED1-GEOM%103%EA/A110/NAF1%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%30/30/43</t>
+  </si>
+  <si>
+    <t>TE 156%INTRODUCTION TO COMMUNICATION NETWORKS%Agyemang Justice Owusu%ED1-TEL%130%NEB-TF%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%130</t>
+  </si>
+  <si>
+    <t>AE 352%SOIL MECHANICS APPLICATION TO MECHANISATION%Agodzo Sampson Kwaku%ED3-AE%101%VSLA/RMA/304/206%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/21/20/20</t>
+  </si>
+  <si>
+    <t>AME 482%SPECIAL VEHICLE DESIGN%Ayetor Godwin Kafui Kwesi%ED4-AUTO%32%LT/206%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/12</t>
+  </si>
+  <si>
+    <t>EE 366%POWER ELECTRONICS%Effah Francis Boafo%ED3-EE%240%PB001/PB014/PB020/PB201/PB214/PB008/PB212%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/38/38/28/22</t>
+  </si>
+  <si>
+    <t>METE 154%ENVIRONMENTAL SCIENCE%Koomson Bennetta%ED1-METE%75%NEB-SF%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%75</t>
+  </si>
+  <si>
+    <t>METE 154%ENVIRONMENTAL SCIENCE%Koomson Bennetta%ED1-MSE%100%303/304/N2%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%30/20/20</t>
+  </si>
+  <si>
+    <t>METE 256%ASSAYING%Koomson Bennetta%ED2-METE%57%RMA/RMB/N2%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/20/17</t>
+  </si>
+  <si>
+    <t>GE 464%DATABASE SYSTEMS%Ayer John Wise Divine%ED4-GEOM%93%N1/303/VSLA%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%25/30/38</t>
+  </si>
+  <si>
+    <t>EE 466%POWER SYSTEMS PLANNING AND OPTIMIZATION%Antoh Emmanuel Kwaku%ED4-EE%165%PB001/PB014/PB020/PB208/PB212%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/28/23</t>
+  </si>
+  <si>
+    <t>TE 358%DIGITAL COMMUNICATION SYSTEMS%Affum Emmanuel Ampoma%ED3-TEL%140%PB201/PB214/PB008/PB208%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/40/30/30</t>
+  </si>
+  <si>
+    <t>AE 458%CROP LOSSES AND THEIR CONTROL%Darko Joseph Ofei %ED4-AE%103%NAF1/EA/A110%Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%43/30/30</t>
+  </si>
+  <si>
+    <t>GED 254%ROCK ENGINEERING%Gidigasu Solomon Senyo Robert%ED2-GEOL%150%NEB-SF/NEB-FF1/NEB-FF2 %Wednesday, 8 July 2026%Session, 4 (1:30 PM - 2:30 PM)%80/50/20</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-EE%150%PB001/PB014/PB020/PB201%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%38/38/38/36</t>
+  </si>
+  <si>
+    <t>ECON 152%ELEMENTS OF ECONOMICS II%Edward Yeboah%ED3-GEOM%15%206%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%15</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED1-CE%32%PB214%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%32</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Beatrice Sarpong-Danquah%ED1-GEOL%30%PB208%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30</t>
+  </si>
+  <si>
+    <t>ECON 152%ELEMENTS OF ECONOMICS II%Paul Owusu Takyi%ED2-BME%20%VCR%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED2-COE%40%RMB/RMA %Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/20</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-TEL%30%206%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED3-CHE%80%NEB-FF2/NEB-FF1%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/50</t>
+  </si>
+  <si>
+    <t>MSE 256%INTRODUCTION TO POLYMERIC MATERIALS%Asare Eric Kwame Anokye%ED2-MSE%83%PB008/PB212/PB208%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/25/28</t>
+  </si>
+  <si>
+    <t>CHE 252%CHEMICAL PROCESS CALCULATIONS II%Ohemeng-Boahen Godfred%ED2-PCE%65%NEB-FF2/NEB-FF1%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%25/40</t>
+  </si>
+  <si>
+    <t>CHE 252%CHEMICAL PROCESS CALCULATIONS II%Rockson Mizpah Ama Dziedzorm%ED2-CHE%160%VSLA/303/N1/LT/N2/304%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/30/25/25/20/17</t>
+  </si>
+  <si>
+    <t>EE 156%ELECTRICAL ENG. DRAWING%Kwegyir Daniel%ED1-EE%295%NEB-TF/NEB-SF%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%147/148</t>
+  </si>
+  <si>
+    <t>CE 264%INTRO TO ENVIRONMENTAL ENG.%Essandoh Helen Michelle Korkor%ED2-CE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB212%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/40/40/40/30/20</t>
+  </si>
+  <si>
+    <t>AE 158%INTRODUCTION TO INFORMATION TECHNOLOGY%Bessah Enoch%ED1-AE%128%EA/A110/VCR/NAF1%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/30/25/43</t>
+  </si>
+  <si>
+    <t>GED 366%MINERAL ECONOMICS AND EVALUATION%Foli Gordon%ED3-GEOL%154%VSLA/RMB/N1/LT/N2/304%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/24/24/24/20/17</t>
+  </si>
+  <si>
+    <t>PHY 170%GENERAL PHYSICS%Boateng Cyril Dziedzorm%ED1-PE%130%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%130</t>
+  </si>
+  <si>
+    <t>PHY 170%GENERAL PHYSICS%Boateng Cyril Dziedzorm%ED1-CHE%120%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%120</t>
+  </si>
+  <si>
+    <t>PHY 170%GENERAL PHYSICS%Abavare Eric Kwabena Kyeh%ED1-PCE%56%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%56</t>
+  </si>
+  <si>
+    <t>AERO 274%AEROSPACE DESIGN PROJECT II%Andoh Prince Yaw%ED2-AERO%75%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%75</t>
+  </si>
+  <si>
+    <t>AME 274%AUTOMOTIVE DESIGN PROJECT%Andoh Prince Yaw%ED2-AUTO%82%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%82</t>
+  </si>
+  <si>
+    <t>IE 274%SECOND YEAR DESIGN PROJECT%Andoh Prince Yaw%ED2-IND%80%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%80</t>
+  </si>
+  <si>
+    <t>MME 274%MARINE ENGINEERING DESIGN PROJECT II%Andoh Prince Yaw%ED2-MARI%37%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%37</t>
+  </si>
+  <si>
+    <t>ME 274%MACHINE DESIGN PROJECT%Andoh Prince Yaw%ED2-ME%240%Computer Based%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%240</t>
+  </si>
+  <si>
+    <t>IE 368%OPERATIONS RESEARCH II%Asiedu Charlotte%ED3-IND%70%RMA/RMB/206%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%24/24/22</t>
+  </si>
+  <si>
+    <t>CHE 370%ENVIRONMENTAL IMPACT ASSESSMENT%Afotey Benjamin%ED3-PCE%30%A110%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30</t>
+  </si>
+  <si>
+    <t>ME 472%MACHINE SHOP AND FACTORY DESIGN%Obeng George Yaw%ED4-ME%54%PB008/PB208 %Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%27/27</t>
+  </si>
+  <si>
+    <t>ME 472%MACHINE SHOP AND FACTORY DESIGN%Obeng George Yaw%ED4-AERO%52%N1/303 %Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%25/27</t>
+  </si>
+  <si>
+    <t>ME 164%ENGINEERING MECHANICS I: STATICS%Dzebre Denis Edem Kwame%ED1-ME%225%PB001/PB014/PB020/PB201/PB214/PB208 %Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%39/39/39/39/39/30</t>
+  </si>
+  <si>
+    <t>ME 164%STATICS OF SOLID MECHANICS%Dzebre Denis Edem Kwame%ED1-AERO%70%RMA/RMB/206%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%24/24/22</t>
+  </si>
+  <si>
+    <t>PE 452%PETROLEUM PROJECT EVALUATION%Sarkodie Kwame%ED4-PE%99%EA/A110/NAF1%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%28/28/43</t>
+  </si>
+  <si>
+    <t>MSE 362%MATERIALS JOINING PROCESSES%Kwofie Samuel%ED3-METE%87%N1/304/VSLA%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%25/20/42</t>
+  </si>
+  <si>
+    <t>MSE 362%MATERIALS JOINING PROCESSES%Kwofie Samuel%ED3-MSE%85%NEB-FF1/NEB-FF2%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%55/30</t>
+  </si>
+  <si>
+    <t>PE 360%WELL TESTING%Adenutsi Caspar Daniel%ED3-PE%80%NEB-FF2/NEB-FF1%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/50</t>
+  </si>
+  <si>
+    <t>GED 468%GEOSTATISTICS%Nuamah Daniel Oduro Boatey%ED4-GEOL%72%303/VSLA%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/42</t>
+  </si>
+  <si>
+    <t>MME 462%MARINE CONTROL ENGINEERING AND AUTOMATION%Adjei Eunice Akyereko%ED4-MARI%23%VCR%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%23</t>
+  </si>
+  <si>
+    <t>EE 156%ELECTRICAL ENG. DRAWING%Kwegyir Daniel%ED1-COE%262%NEB-SF/NEB-TF%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%85/177</t>
+  </si>
+  <si>
+    <t>PE 252%HEAT TRANSPORT PROCESSES%Adjei Stephen%ED2-PE%95%NEB-SF%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%95</t>
+  </si>
+  <si>
+    <t>CE 376%QUANTITIES AND COST ESTIMATION IN CIVIL ENGINEERING%Osei Jack Banahene%ED3-CE%230%PB001/PB014/PB020/PB201/PB214/PB008%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/40/40/40/40/30</t>
+  </si>
+  <si>
+    <t>BME 362%BIOMATERIALS I%Odame Prince%ED3-BME%90%NAF1/EA/VCR%Wednesday, 8 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/30/20</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Lawton Adu-Ansah%ED1-GEOM%103%EA/A110/NAF1%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%30/30/43</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Lawton Adu-Ansah%ED1-AUTO%85%RMB/RMA/206/N2%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%23/22/20/20</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Lawton Adu-Ansah%ED1-TEL%130%NEB-TF/NEB-FF1%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%80/50</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Lawton Adu-Ansah%ED1-ME%225%PB001/PB014/PB020/PB201/PB214/PB212%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/40/40/40/40/25</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Isaac Azure%ED1-CHE%120%VSLA/303/N1/206%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/25/20</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS OF SEVERAL VARIABLES%Isaac Azure%ED1-PCE%56%PB008/PB208%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%28/28</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Ezearn Jeffery%ED1-AERO%70%LT/304/N1%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%25/20/25</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Ezearn Jeffery%ED1-IND%83%N2/304/VSLA%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%20/20/43</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Ezearn Jeffery%ED1-MARI%46%RMA/RMB%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%23/23</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH SEVERAL VARIABLES%Ezearn Jeffery%ED1-CE%245%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%84/84/52/25</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Ezearn Jeffery%ED1-COE%262%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%38/38/38/37/37/27/27/20</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Isaac Azure%ED1-METE%75%303/LT/304%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%30/25/20</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Isaac Azure%ED1-MSE%100%NEB-SF/NEB-FF2%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%80/20</t>
+  </si>
+  <si>
+    <t>AE 356%FARM POWER AND MACHINERY%Aikins Stephen Hill Mends%ED3-AE%101%A110/EA/NAF1%Thursday, 9 July 2026%Session, 1 (8:15 AM - 9:15 AM)%29/29/43</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Ayekple Yao Elikem%ED1-EE%295%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212/NEB-FF2%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/38/28/27/25/25</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH ANALYSIS%Kwabi Prince Amponsah%ED1-PE%130%VSLA/303/N1/LT/N2%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/30/25/25/10</t>
+  </si>
+  <si>
+    <t>MATH 152%CALCULUS WITH SEVERAL VARIABLES%Kwabi Prince Amponsah%ED1-GEOL%125%VCR/EA/A110/NAF1%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%25/30/30/40</t>
+  </si>
+  <si>
+    <t>CHE 358%NUMERICAL METHODS FOR CHEMICAL ENGINEERS%Mensah Mary%ED3-PCE%53%NEB-FF1%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%53</t>
+  </si>
+  <si>
+    <t>CHE 358%NUMERICAL METHODS FOR CHEMICAL ENGINEERS%Mensah Mary%ED3-CHE%105%VCR/EA/A110/NAF1%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/25/25/35</t>
+  </si>
+  <si>
+    <t>PE 260%RESERVOIR FLUID PROPERTIES%Casper Daniel Adenutsi%ED2-PE%95%LT/RMB/RMA/N2/304%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%25/20/20/20/10</t>
+  </si>
+  <si>
+    <t>COE 272%DIGITAL SYSTEMS DESIGN I%Nunoo-Mensah Henry%ED2-COE%255%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%37/37/37/37/37/26/27/20</t>
+  </si>
+  <si>
+    <t>COE 272%DIGITAL SYSTEMS DESIGN I%Nunoo-Mensah Henry%ED2-BME%80%NEB-FF2/NEB-FF1%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/50</t>
+  </si>
+  <si>
+    <t>ME 374%MACHINE ELEMENTS DESIGN II%Andoh Prince Yaw%ED3-ME%222%NEB-TF/NEB-SF%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%170/52</t>
+  </si>
+  <si>
+    <t>CHE 256%HEAT TRANSPORT PROCESSES%Ohemeng-Boahen Godfred%ED2-PCE%65%VSLA/304 %Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%45/20</t>
+  </si>
+  <si>
+    <t>PE 362%GEOSTATISTICS%Mustapha Hameed%ED3-PE%80%NEB-SF%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%80</t>
+  </si>
+  <si>
+    <t>PE 458%OILFIELD GEOLCHEMISTRY%Adenutsi Caspar Daniel%ED4-PE%99%303/RMA/RMB/N1%Thursday, 9 July 2026%Session, 2 (10:00 AM - 11:00 AM)%30/24/24/21</t>
+  </si>
+  <si>
+    <t>CE 258%STRUCTURAL ANALYSIS%Kankam Charles Kwame%ED2-CE%250%PB001/PB020/PB014/PB201/PB214/PB008/PB212%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/20</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Benedict Barnes%ED2-CHE%160%NEB-TF/NEB-SF%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%80/80</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Emmanuel Mensah%ED2-EE%340%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212/NEB-FF1%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/30/25/55</t>
+  </si>
+  <si>
+    <t>TE 256%COMMUNICATION CIRCUITS%Abdul-Rahman Ahmed%ED2-TEL%175%VSLA/LT/RMA/RMB/206/303/304/N1%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/22/22/22/22/25/20/20</t>
+  </si>
+  <si>
+    <t>EE 362%SUBSTATIONS AND TRANSMISSION LINE DESIGN%Antoh Emmanuel Kwaku%ED3-EE%240%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%85/85/55/20</t>
+  </si>
+  <si>
+    <t>AERO 256%AEROSPACE STRUCTURES%Agyei Agyemang Anthony%ED2-AERO%75%NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/30</t>
+  </si>
+  <si>
+    <t>ME 262%THEORY OF MACHINES%Adam Faisal Wahib%ED2-AE%155%VSLA/LT/RMA/RMB/206/303%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/25/22/22/22/25</t>
+  </si>
+  <si>
+    <t>MSE 456%MATERIALS QUALITY CONTROL, ASSURRANCE AND SELECTION%Arthur Emmanuel Kwesi%ED4-MSE%60%NAF1/EA%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/20</t>
+  </si>
+  <si>
+    <t>MSE 456%MATERIALS QUALITY CONTROL, ASSURRANCE AND SELECTION%Arthur Emmanuel Kwesi%ED4-METE%55%A110/VCR%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%30/25</t>
+  </si>
+  <si>
+    <t>GED 462%ECONOMIC GEOLLOGY%Mensah Emmanuel%ED4-GEOL%95%NAF1/EA/VCR%Thursday, 9 July 2026%Session, 3 (11:45 AM - 12:45 PM)%45/30/20</t>
+  </si>
+  <si>
+    <t>CHE 458%ENTREPRENEURSHIP AND BUSINESS DEVELOPMENT%Asamoah Boateng Kenneth%ED4-CHE%114%NAF1/EA/A110/VCR%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/25/25/24</t>
+  </si>
+  <si>
+    <t>CHE 458%ENTREPRENEURSHIP AND BUSINESS DEVELOPMENT%Asamoah Boateng Kenneth%ED4-PCE%55%206/303/304%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/25/10</t>
+  </si>
+  <si>
+    <t>AE 452%SOIL AND WATER ENGINEERING II%Agyare Wilson Agyei%ED4-AE%103%VSLA/LT/RMA/RMB%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/23/22/20</t>
+  </si>
+  <si>
+    <t>TE 352%DATA COMMUNICATION PRINCIPLES%Gadze James Dzisi%ED3-TEL%140%NEB-TF/NEB-SF%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%70/70</t>
+  </si>
+  <si>
+    <t>GE 362%PRINCIPLES OF GIS%Forkuo Eric Kwabena%ED3-GEOM%122%NAF1/EA/A110/VCR%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%45/30/30/22</t>
+  </si>
+  <si>
+    <t>CE 456%STRUCTURAL DYNAMICS%Mark Adom-Asamoah%ED4-CE%95%PB201/PB214/PB212%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/40/15</t>
+  </si>
+  <si>
+    <t>IE 454%PRODUCTION PLANNING AND CONTROL%Dzebre Denis Edem Kwame%ED4-IND%69%PB014/PB008%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%39/30</t>
+  </si>
+  <si>
+    <t>AME 386%MANUAL POWER TRAIN%Abu Frimpong Solomon%ED3-AUTO%40%303/304%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%20/20</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-IND%80%NEB-TF%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%80</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-AUTO%82%NEB-SF%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%82</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-MARI%37%PB020%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%37</t>
+  </si>
+  <si>
+    <t>MSE 252%HEAT AND MASS TRANSPORT%Agyemang Frank Ofori%ED2-MSE%83%NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%53/30</t>
+  </si>
+  <si>
+    <t>MSE 252%HEAT AND MASS TRANSPORT%Agyemang Frank Ofori%ED2-METE%57%PB001/PB208%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%37/20</t>
+  </si>
+  <si>
+    <t>ME 452%FLUID MACHINERY%Opoku Richard%ED4-ME%80%NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%50/30</t>
+  </si>
+  <si>
+    <t>ME 376%INTRODUCTION TO CAD/CAM%Afriyie Nyarko Frank Kwabena%ED3-AE%101%PB001/PB020/PB008%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/40/21</t>
+  </si>
+  <si>
+    <t>IE 358%COMPUTER-AIDED DESIGN AND MANUFACTURING%Afriyie Nyarko Frank Kwabena%ED3-IND%70%PB201/PB208%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/30</t>
+  </si>
+  <si>
+    <t>AME 496%VEHICLE MAINTENANCE AND REGULATION%Abu Frimpong Solomon%ED4-AUTO%32%PB014%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%32</t>
+  </si>
+  <si>
+    <t>AERO 456%APPLIED METEOROLOGY%Prince Junior Asilevi%ED4-AERO%61%PB214/PB212%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/23</t>
+  </si>
+  <si>
+    <t>GE 262%PRINCIPLES OF REMOTE SENSING%Yaw Mensah Asare%ED2-GEOM%132%VSLA/LT/RMA/RMB/206%Thursday, 9 July 2026%Session, 4 (1:30 PM - 2:30 PM)%45/25/24/20/20</t>
+  </si>
+  <si>
+    <t>GE 476%PROFESSIONAL STUDIES AND DEVELOPMENT%Akrofi Emmanuel Offei%ED4-GEOM%93%NAF1/EA/VCR%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/30/20</t>
+  </si>
+  <si>
+    <t>TE 454%DIGITAL SIGNAL PROCESSING%Kponyo Jerry John%ED4-TEL%138%VSLA/LT/RMA/RMB/206%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/25/24/24/20</t>
+  </si>
+  <si>
+    <t>EE 472%DIGITAL SIGNAL PROCESSING%Kponyo Jerry John%ED4-EE%12%PB212%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%12</t>
+  </si>
+  <si>
+    <t>CHE 366%RENEWABLE ENERGY RESOURCES%Baah-Ennumh Emmanuel Kwaku%ED3-PCE%20%PB208%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20</t>
+  </si>
+  <si>
+    <t>GED 258%OPTICAL MINERALOGY%Wilson Matthew Coffie%ED2-GEOL%150%VSLA/LT/RMA/RMB/206/303%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/25/22/22/22/20</t>
+  </si>
+  <si>
+    <t>CE 368%HIGHWAY ENGINEERING%Tutu Kenneth Adomako%ED3-CE%230%PB001/PB020/PB014/PB201/PB214/PB008%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/40/40/40/30</t>
+  </si>
+  <si>
+    <t>PHY 154%PROPERTIES OF MATTER%Reginald Mensah Noye%ED1-BME%136%NAF1/EA/A110/VCR/303%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/28/28/23/20</t>
+  </si>
+  <si>
+    <t>COE 356%INTRODUCTION TO SOFTWARE ENG.%Adjaidoo Theresa-Samuelle Maame Atwemaah%ED3-COE%265%NEB-TF/NEB-SF%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%175/90</t>
+  </si>
+  <si>
+    <t>PE 364%OIL &amp; GAS GEOLPHYSICS%Quaye Jonathan Atuquaye%ED3-PE%80%NEB-SF%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%80</t>
+  </si>
+  <si>
+    <t>AERO 368%PROPULSION%Bofah Kwasi Kete%ED3-AERO%76%NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%53/23</t>
+  </si>
+  <si>
+    <t>METE 356%THIRD YEAR DESIGN PROJECT%Bota Osei Sekyere%ED3-METE%87%A110/304/N1%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/25/32</t>
+  </si>
+  <si>
+    <t>MSE 396%THIRD YEAR DESIGN PROJECT%Bota Osei Sekyere%ED3-MSE%85%NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%55/30</t>
+  </si>
+  <si>
+    <t>ME 352%FLUID DYNAMICS  II%A. K. Sunnu%ED3-ME%222%PB001/PB020/PB014/PB201/PB214/PB008%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/40/40/40/22</t>
+  </si>
+  <si>
+    <t>ME 352%FLUID DYNAMICS II%Tay Godwin Fabiola Kwaku%ED3-MARI%40%PB208/PB212%Thursday, 9 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/20</t>
+  </si>
+  <si>
+    <t>COE 472%DIGITAL SIGNAL PROCESSING%Adjei Prince Ebenezer%ED4-BME%87%NAF1/EA/VCR%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/27/20</t>
+  </si>
+  <si>
+    <t>AERO 174%AEROSPACE DESIGN PROJECT I%Afriyie Nyarko Frank Kwabena%ED1-AERO%70%303/304/N1%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/20/20</t>
+  </si>
+  <si>
+    <t>ARC 156%INTRODUCTION TO LIGHTING AND ACOUSTICS%Amos-Abanyie Samuel%ED1-CE%55%A110/VCR%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/25</t>
+  </si>
+  <si>
+    <t>PE 254%DRAWING FOR ENGINEERS%Jones Twumasi%ED2-PE%95%NAF1/EA/A110%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%45/25/25</t>
+  </si>
+  <si>
+    <t>EE 188%ELECTRICAL MEASUREMENT AND INSTRUMENTATION%Obeng Kwakye Kingsford Sarkodie%ED1-TEL%130%VSLA/LT/RMA/RMB/206%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%45/25/20/20/20</t>
+  </si>
+  <si>
+    <t>EE 288%ELECTRICAL MEASUREMENT AND INSTRUMENTATION%Klogo Griffith Selorm%ED2-COE%255%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%85/85/55/30</t>
+  </si>
+  <si>
+    <t>CHE 364%PACKAGING TECHNOLOGY%Baah-Ennumh Emmanuel Kwaku%ED3-CHE%45%PB014/PB212%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/15</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Peter Oppong Tawiah%ED1-MSE%100%PB001/PB020/PB008%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%38/38/24</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%A. K. Sunnu%ED1-ME%225%PB001/PB020/PB014/PB201/PB214/PB008%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/40/40/40/40/25</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Sekyere Charles Kofi Kafui%ED1-AUTO%85%NEB-TF%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%85</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Sekyere Charles Kofi Kafui%ED1-MARI%46%NEB-FF1%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%46</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Sekyere Charles Kofi Kafui%ED1-IND%83%NEB-SF%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%83</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Aveyire Joseph%ED1-AE%128%VSLA/LT/RMA/RMB/206%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%42/23/22/21/20</t>
+  </si>
+  <si>
+    <t>ME 160%ENGINEERING DRAWING%Aveyire Joseph%ED1-METE%75%303/304/N1%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%30/20/25</t>
+  </si>
+  <si>
+    <t>GE 162%LARGE SCALE SURVEYING%Ayer John Wise Divine%ED1-GEOM%103%PB201/PB214/PB208%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/40/23</t>
+  </si>
+  <si>
+    <t>PE 476%ENERGY AND CLIMATE CHANGE%Sokama-Neuyam Yen Adams%ED4-PE%22%PB212%Thursday, 9 July 2026%Session, 6 (5:00 PM - 6:00 PM)%22</t>
+  </si>
+  <si>
+    <t>COE 472%DIGITAL SIGNAL PROCESSING%Akowuah Emmanuel Kofi%ED4-COE%160%Computer Based%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%160</t>
+  </si>
+  <si>
+    <t>ACF 256%FINANCIAL ACCOUNTING II%Yeboah Edward%ED2-COE%65%NEB-SF%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%65</t>
+  </si>
+  <si>
+    <t>ACF 256%FINANCIAL ACCOUNTING II%Yeboah Edward%ED2-TEL%40%NEB-FF1%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40</t>
+  </si>
+  <si>
+    <t>CSM 158%FINANCIAL ACCOUNTING II%Yeboah Edward%ED2-BME%18%304%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%18</t>
+  </si>
+  <si>
+    <t>CSM 158%ACCOUNTING II%Beatrice Sarpong-Danquah%ED3-GEOM%35%NEB-FF2%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%35</t>
+  </si>
+  <si>
+    <t>CSM 158%PRINCIPLES OF ACCOUNTING II%John Bosco Dramani%ED1-GEOL%5%PB212%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%5</t>
+  </si>
+  <si>
+    <t>PE 468%PETROLEUM BUSINESS: STRUCTURES, LOGISTICS%Quaye Jonathan Atuquaye%ED4-PE%77%NEB-TF%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%77</t>
+  </si>
+  <si>
+    <t>COE 152%BASIC ELECTRONICS%Addo Daniel Akwei%ED1-BME%136%NEB-SF/NEB-FF1%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%85/51</t>
+  </si>
+  <si>
+    <t>COE 152%BASIC ELECTRONICS%Klogo Griffith Selorm%ED1-COE%262%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%38/38/38/38/38/28/24/20</t>
+  </si>
+  <si>
+    <t>EE 368%POWER SYSTEMS ANALYSIS%Twumasi Elvis%ED3-EE%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%38/38/38/38/38/28/22</t>
+  </si>
+  <si>
+    <t>GED 342%MINING PRINCIPLES AND SYSTEMS%Owusu-Sarpong Seth%ED3-GEOL%154%VSLA/LT/RMA/RMB/206/303%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%40/25/22/22/22/25</t>
+  </si>
+  <si>
+    <t>TE 152%ENGINEERING RESEARCH AND TECHNICAL REPORT WRITING%Obeng Kwakye Kingsford Sarkodie%ED1-TEL%130%NAF1/EA/A110/VCR%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/30/25</t>
+  </si>
+  <si>
+    <t>PE 154%INTRODUCTION TO PETROLEUM ENGINEERING%Erzuah Samuel%ED1-PE%130%NAF1/EA/A110/VCR%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/30/30/25</t>
+  </si>
+  <si>
+    <t>MSE 358%NUMERICAL METHODS FOR ENGINEERS%Nartey Martinson Addo%ED3-MSE%85%RMB/206/303/304%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%22/22/26/15</t>
+  </si>
+  <si>
+    <t>MSE 358%NUMERICAL METHODS FOR ENGINEERS%Nartey Martinson Addo%ED3-METE%87%VSLA/LT/RMA%Friday, 10 July 2026%Session, 1 (8:15 AM - 9:15 AM)%45/20/22</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-BME%80%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%80</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-AUTO%82%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%82</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PCE%65%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%65</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PE%95%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%95</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-MSE%83%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%83</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-METE%57%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%57</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AERO%75%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%75</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-IND%80%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%80</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-TEL%175%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%175</t>
+  </si>
+  <si>
+    <t>MATH 252%ANALYSIS IV%Wireko Fredrick Asenso%ED2-GEOL%150%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%150</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Reindorf Nartey Borkor%ED2-CE%250%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%250</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AE%155%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%155</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-COE%255%Computer Based%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%255</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-GEOM%132%VSLA/LT/RMA/RMB/206%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%42/24/24/22/20</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Boateng Maxwell Akwasi%ED2-MARI%37%NAF1%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/17</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Boateng Maxwell Akwasi%ED2-ME%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%38/38/38/38/38/28/22</t>
+  </si>
+  <si>
+    <t>EE 262%AC MACHINES%Asigri Peter%ED2-EE%340%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212/NEB-FF1%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/40/40/40/40/30/30/25/55</t>
+  </si>
+  <si>
+    <t>AME 356%LAND VEHICLE STRUCTURES%Ayetor Godwin Kafui Kwesi%ED3-AUTO%40%303/206%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%20/20</t>
+  </si>
+  <si>
+    <t>PE 354%DRILLING ENGINEERING II%Erzuah Samuel%ED3-PE%80%NEB-SF%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%80</t>
+  </si>
+  <si>
+    <t>AERO 374%AIRCRAFT PERFORMANCE AND DESIGN%Agyei Agyemang Anthony%ED3-AERO%76%EA/A110/VCR%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%28/28/20</t>
+  </si>
+  <si>
+    <t>AME 476%MODERN AUTOMOBILE TECHNOLOGY%Ayetor Godwin Kafui Kwesi%ED4-AUTO%32%NEB-TF%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%32</t>
+  </si>
+  <si>
+    <t>TE 456%SATELLITE COMMUNICATION AND NAVIGATION SYSTEMS%Gadze James Dzisi%ED4-TEL%138%NEB-TF%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%138</t>
+  </si>
+  <si>
+    <t>AE 464%CROP STORAGE AND STORAGE STRUCTURES%Bart Plange Ato%ED4-AE%103%VSLA/LT/RMA/RMB%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40/23/20/20</t>
+  </si>
+  <si>
+    <t>TE 372%ENGINEERING PROJECT DESIGN AND MANAGEMENT%Agyekum Kwame Agyeman-Prempeh%ED3-TEL%140%NEB-SF/NEB-FF1%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%85/55</t>
+  </si>
+  <si>
+    <t>MME 486%SHIP SAFETY, ENVIRONMENTAL PROTECTION AND SAFE WATCH KEEPING%Larkai Francis Laako%ED4-MARI%23%EA%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%23</t>
+  </si>
+  <si>
+    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-AERO%5%VCR%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%5</t>
+  </si>
+  <si>
+    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-ME%40%NAF1%Friday, 10 July 2026%Session, 2 (10:00 AM - 11:00 AM)%40</t>
+  </si>
+  <si>
+    <t>AE 362%RESEARCH METHODS FOR ENGINEERS%Amponsah William%ED3-AE%101%VSLA/LT/RMA/RMB%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/23/20/20</t>
+  </si>
+  <si>
+    <t>CE 468%TRANSPORTATION ENGINEERING%Tuffour Yaw Adubofour%ED4-CE%150%VSLA/LT/RMA/RMB/206/303%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/25/22/22/22/21</t>
+  </si>
+  <si>
+    <t>GE 474%PRINCIPLES OF VALUATION OF LAND AND BUILDING%Ayitey Jonathan%ED4-GEOM%93%NAF1/EA/VCR%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%43/30/20</t>
+  </si>
+  <si>
+    <t>AE 162%BASIC AGRICULTURE%Bessah Enoch%ED1-AE%128%NAF1/EA/A110/VCR%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%44/30/30/24</t>
+  </si>
+  <si>
+    <t>PETE 354%PETROLEUM PRODUCTION ENGINEERING%Ankudey Emmanuel Godwin%ED3-PCE%53%NEB-FF1%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%53</t>
+  </si>
+  <si>
+    <t>BME 372%BIOINSTRUMENTATION I%Acquah Isaac%ED3-BME%90%A110/206/303/N1%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%24/22/24/20</t>
+  </si>
+  <si>
+    <t>IE 360%QUALITY ASSURANCE%Sackey Samuel Mensah%ED3-IND%70%NEB-FF1/NEB-FF2%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%50/20</t>
+  </si>
+  <si>
+    <t>CE 360%FOUNDATION ENGINEERING%Acquaah Vincent Kofi Abaka%ED3-CE%230%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30</t>
+  </si>
+  <si>
+    <t>ME 370%MANUFACTURING TECHNOLOGY%Francis Davis%ED3-ME%222%PB001/PB020/PB014/PB201/PB214/PB008/PB208%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/22</t>
+  </si>
+  <si>
+    <t>COE 368%DATABASE AND INFORMATION RETRIEVAL%Keelson Eliel%ED3-COE%265%NEB-TF/NEB-SF%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%133/132</t>
+  </si>
+  <si>
+    <t>GED 466%PETROLEUM GEOLOGY%Foli Gordon%ED4-GEOL%35%N1/N2%Friday, 10 July 2026%Session, 3 (11:45 AM - 12:45 PM)%20/15</t>
+  </si>
+  <si>
+    <t>CHE 254%CHEMICAL ENGINEERING THERMODYNAMICS II%Bonsu Jude Kwaku%ED2-CHE%160%VSLA/LT/RMA/RMB/206/303%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%43/25/23/23/23/23</t>
+  </si>
+  <si>
+    <t>TE 386%DIGITAL COMMUNICATION SYSTEMS%Charles Mawutor Adrah%ED3-EE%240%NEB-TF/NEB-SF%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%120/120</t>
+  </si>
+  <si>
+    <t>MME 386%MARINE ELECTRICAL TECHNOLOGY AND ELECTRICAL MEASUREMENTS%Frimpong Emmanuel Asuming%ED3-MARI%40%PB001%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40</t>
+  </si>
+  <si>
+    <t>AME 156%BASIC THERMODYNAMICS%Samuel Boahen%ED1-AUTO%85%PB020/PB014/PB008%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/30/19</t>
+  </si>
+  <si>
+    <t>GED 354%PRINCIPLES OF GEOPHYSICS%Ali Bukari%ED3-GEOL%154%VSLA/LT/RMA/RMB/206/303%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%45/25/24/20/20/20</t>
+  </si>
+  <si>
+    <t>MSE 356%ENGINEERING PROPERTIES OF POLYMERS%Asare Eric Kwame Anokye%ED3-MSE%85%NEB-FF1/A110%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%55/30</t>
+  </si>
+  <si>
+    <t>TE 472%MOBILE AND SATELLITE COMMUNICATION SYSTEM%Gadze James Dzisi%ED4-EE%4%VCR%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%4</t>
+  </si>
+  <si>
+    <t>EE 166%CIRCUIT THEORY%Twumasi Elvis%ED1-EE%295%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212/NEB-FF2%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%38/38/38/38/38/28/28/24/25</t>
+  </si>
+  <si>
+    <t>MSE 152%KINETICS OF CHEMICAL REACTIONS%Patrick Aggrey%ED1-MSE%100%NAF1/EA/A110%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/30/30</t>
+  </si>
+  <si>
+    <t>METE 152%CHEMISTRY FOR METALLURGICAL ENGINEERS%Patrick Aggrey%ED1-METE%75%NEB-FF1/NEB-FF2%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%55/20</t>
+  </si>
+  <si>
+    <t>METE 454%METALLURGICAL WASTE MANAGEMENT%Koomson Bennetta%ED4-METE%55%PB201/PB208%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%35/20</t>
+  </si>
+  <si>
+    <t>MSE 452%WASTE MANAGEMENT%Koomson Bennetta%ED4-MSE%60%PB214/PB212%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%40/20</t>
+  </si>
+  <si>
+    <t>PE 456%WELL COMPLETION AND STIMULATION%Erzuah Samuel%ED4-PE%99%NAF1/EA/VCR%Friday, 10 July 2026%Session, 4 (1:30 PM - 2:30 PM)%45/30/24</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Boakye-Agyeman Candy%ED2-TEL%103%NAF1/EA/A110%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%43/30/30</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Alexander Ocloo%ED3-CHE%55%303/N1%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%30/25</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION  II%Pharis Jeel Darko%ED3-GEOM%65%NEB-FF1/NEB-FF2%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/25</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Alexander Ocloo%ED2-EE%170%PB001/PB020/PB014/PB008/PB212%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/40/30/20</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Boakye-Agyeman Candy%ED1-GEOL%90%NAF1/EA/VCR%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/25/20</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Boakye-Agyeman Candy%ED1-CE%160%PB001/PB020/PB014/PB201%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/40/40</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Boakye-Agyeman Candy%ED1-MARI%46%A110/VCR%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%26/20</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION II%Pharis Jeel Darko%ED2-BME%43%304/N2%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/23</t>
+  </si>
+  <si>
+    <t>FC 182%FRENCH FOR COMMUNICATION%Pharis Jeel Darko%ED2-COE%150%VSLA/LT/RMA/RMB/206/303%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/25/20/20/20/20</t>
+  </si>
+  <si>
+    <t>GE 284%HYDROGRAPHIC SURVEYING AND MARINE SCIENCE%Asante Cosmas Yaw%ED2-GEOM%132%VSLA/LT/RMA/RMB/206%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/25/24/23/20</t>
+  </si>
+  <si>
+    <t>ME 464%INSTRUMENTATION%Adam Faisal Wahib%ED4-ME%135%PB201/PB214/PB208/PB212%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40/40/30/25</t>
+  </si>
+  <si>
+    <t>METE 254%ORE BENEFICIATION%Koomson Bennetta%ED2-METE%57%304/N1/N2%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%20/20/17</t>
+  </si>
+  <si>
+    <t>AERO 492%AEROSPACE SAFETY AND AIR SECURITY%Peter Oppong Tawiah %ED4-AERO%61%PB214/PB208%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%36/25</t>
+  </si>
+  <si>
+    <t>AME 256%AUTOMOTIVE CHASSIS%Ayetor Godwin Kafui Kwesi%ED2-AUTO%82%NEB-SF%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%82</t>
+  </si>
+  <si>
+    <t>AME 376%AUTOMOTIVE CHASSIS%Ayetor Godwin Kafui Kwesi%ED3-AUTO%40%NEB-TF%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%40</t>
+  </si>
+  <si>
+    <t>CHE 158%INTRODUCTION TO INFORMATION TECHNOLOGY%Baidoo Martina Francisca%ED1-CHE%120%NEB-TF%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%120</t>
+  </si>
+  <si>
+    <t>PCE 158%INTRODUCTION TO INFORMATION TECHNOLOGY%Baidoo Martina Francisca%ED1-PCE%56%NEB-SF%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%56</t>
+  </si>
+  <si>
+    <t>AERO 362%AIR VEHICLE STABILITY AND CONTROL%Oppong David Kofi%ED3-AERO%76%NEB-SF%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%76</t>
+  </si>
+  <si>
+    <t>PE 350%NUMERICAL METHODS FOR PETROLEUM ENGINEERS%Sokama-Neuyam Yen Adams%ED3-PE%80%NEB-FF1/NEB-FF2%Friday, 10 July 2026%Session, 5 (3:15 PM - 4:15 PM)%50/30</t>
+  </si>
+  <si>
+    <t>GE 158%INTRODUCTION TO INFORMATION TECHNOLOGY%Titus Tienaah%ED1-GEOM%103%EA/A110/NAF1%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%43/30/30</t>
+  </si>
+  <si>
+    <t>CHE 254%CHEMICAL ENGINEERING THERMODYNAMICS II%Eunice Sefakor Aku Dogbe%ED2-PCE%65%304/N2/LT%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%20/25/20</t>
+  </si>
+  <si>
+    <t>PETE 450%NATURAL GAS ENGINEERING%Ankudey Emmanuel Godwin%ED3-PCE%53%PB212/PB208%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%53</t>
+  </si>
+  <si>
+    <t>AERO 362%AIR VEHICLE STABILITY AND CONTROL%Oppong David Kofi%ED3-AERO%76%NEB-TF%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%76</t>
+  </si>
+  <si>
+    <t>ME 266%THERMODYNAMICS I%Amoabeng Kofi Owura%ED2-IND%80%NEB-SF%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%80</t>
+  </si>
+  <si>
+    <t>ME 266%THERMODYNAMICS I%Amoabeng Kofi Owura%ED2-ME%240%PB001/PB014/PB020/PB201/PB214/PB008/PB212%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%38/38/38/38/38/28/22</t>
+  </si>
+  <si>
+    <t>ME 266%THERMODYNAMICS I%Boahen Samuel%ED2-AERO%75%NEB-FF2/NEB-FF1%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%75</t>
+  </si>
+  <si>
+    <t>ME 166%APPLIED THERMODYNAMICS %Amoabeng Kofi Owura%ED1-BME%136%VSLA/RMA/RMB/206/304%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%43/25/24/22/22</t>
+  </si>
+  <si>
+    <t>GE 282%LARGE SCALE SURVEYING%Dadzie Isaac%ED2-CE%250%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%85/85/55/25</t>
+  </si>
+  <si>
+    <t>GE 282%LARGE SCALE SURVEYING%Dadzie Isaac%ED2-GEOL%150%VSLA/303/N1/206/N2%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%45/25/20/20/20/20</t>
+  </si>
+  <si>
+    <t>CE 476%SYSTEM ENGINEERING II%Osei Jack Banahene%ED4-CE%115%NAF1/VCR/EA/A110%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%40/30/25/20</t>
+  </si>
+  <si>
+    <t>GE 286%PRINCIPLES OF SURVEYING%Akwasi Afrifa Acheampong%ED2-AE%155%NEB-SF/NEB-TF%Monday, 6 July 2026%Session, 1 (8:15 AM - 9:15 AM)%78/77</t>
+  </si>
+  <si>
+    <t>COE 158%INTRODUCTION TO INFORMATION TECHNOLOGY%Addo Daniel Akwei%ED1-COE%262%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%38/38/38/38/38/28/24/20</t>
+  </si>
+  <si>
+    <t>GED 464%ENGINEERING MANAGEMENT%Takyi Gabriel%ED4-GEOL%95%303/N1/RMA/RMB%Friday, 10 July 2026%Session, 6 (5:00 PM - 6:00 PM)%25/30/20/20</t>
+  </si>
+  <si>
+    <t>IE 354%LOGISTICS AND SUPPLY CHAIN ENGINEERING%Asiedu Charlotte%ED3-IND%70%NEB-TF%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%70</t>
+  </si>
+  <si>
+    <t>CE 480%FINITE ELEMENT ANALYSIS%Jones Owusu Twumasi%ED4-CE%18%RMA%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%18</t>
+  </si>
+  <si>
+    <t>PE 466%FUNDAMENTALS OF PETROLEUM LAW%Amoah Enoch Kwabena%ED4-PE%99%VSLA/303/LT%Tuesday, 7 July 2026%Session, 5 (3:15 PM - 4:15 PM)%44/30/25</t>
+  </si>
+  <si>
+    <t>TE 458%NETWORK PLANNING AND OPTIMIZATION%Kwasi Adu-Boahen Opare%ED4-TEL%138%NAF1/EA/A110/303%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/30/30/30</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -381,11 +1810,2360 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A469"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="210.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>464</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/src/outputs/2ND SEM TTFINAL_1-cleaned.xlsx
+++ b/src/outputs/2ND SEM TTFINAL_1-cleaned.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB0DBAC-3093-4D5F-B09A-BC849EBEBD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A99A912-A6BA-4788-97E8-DF3AA6945C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,9 +192,6 @@
     <t>PL 252%PLANNING THE PHYSICAL ENVIRONMENT%Aboagye Prince Anokye%ED3-GEOM%122%NAF1/EA/A110/VCR%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%42/30/30/20</t>
   </si>
   <si>
-    <t>TE 262%ELECTROMAGNETIC FIELDS%Kwame Oteng Gyasi%ED2-EE%340%PB001/PB014/PB020/PB201/PB214/PB008/PB208/NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/30/30/50</t>
-  </si>
-  <si>
     <t>TE 254%ELECTROMAGNETIC FIELD THEORY%Kwame Oteng Gyasi%ED2-TEL%175%VSLA/303/N1/N2/304/206/RMA%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/30/25/20/20/20/20</t>
   </si>
   <si>
@@ -1435,6 +1432,9 @@
   </si>
   <si>
     <t>TE 458%NETWORK PLANNING AND OPTIMIZATION%Kwasi Adu-Boahen Opare%ED4-TEL%138%NAF1/EA/A110/303%Wednesday, 8 July 2026%Session, 5 (3:15 PM - 4:15 PM)%45/30/30/30</t>
+  </si>
+  <si>
+    <t>TE 254%ELECTROMAGNETIC FIELDS%Kwame Oteng Gyasi%ED2-EE%340%PB001/PB014/PB020/PB201/PB214/PB008/PB208/NEB-FF2/NEB-FF1%Monday, 6 July 2026%Session, 3 (11:45 AM - 12:45 PM)%40/40/40/40/40/30/30/30/50</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
@@ -2094,2072 +2094,2072 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>468</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
